--- a/251211/NMDAR_Dyskinesia.xlsx
+++ b/251211/NMDAR_Dyskinesia.xlsx
@@ -383,11 +383,11 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9961</v>
+        <v>0.9614</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.978 – 1.0143</t>
+          <t>0.8005 – 1.1522</t>
         </is>
       </c>
       <c r="D2">
@@ -401,11 +401,11 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.9975000000000001</v>
+        <v>0.9748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.9804 – 1.0146</t>
+          <t>0.8206 – 1.1556</t>
         </is>
       </c>
       <c r="D3">
@@ -419,11 +419,11 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.997</v>
+        <v>0.9707</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.981 – 1.0131</t>
+          <t>0.8252 – 1.1388</t>
         </is>
       </c>
       <c r="D4">
@@ -437,11 +437,11 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9948</v>
+        <v>0.9497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9795 – 1.0102</t>
+          <t>0.8128 – 1.1069</t>
         </is>
       </c>
       <c r="D5">
@@ -455,11 +455,11 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.6631</v>
+        <v>1.0522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.374 – 7.3435</t>
+          <t>0.9063 – 1.2206</t>
         </is>
       </c>
       <c r="D6">
@@ -473,11 +473,11 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.1947</v>
+        <v>1.0179</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.308 – 4.5319</t>
+          <t>0.8889 – 1.1631</t>
         </is>
       </c>
       <c r="D7">
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.6924</v>
+        <v>0.9639</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.1832 – 2.5162</t>
+          <t>0.8439 – 1.0967</t>
         </is>
       </c>
       <c r="D8">
@@ -509,11 +509,11 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.6988</v>
+        <v>0.9648</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.1921 – 2.4511</t>
+          <t>0.8479 – 1.0938</t>
         </is>
       </c>
       <c r="D9">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9976</v>
+        <v>0.976</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.9773 – 1.0179</t>
+          <t>0.7952 – 1.1937</t>
         </is>
       </c>
       <c r="D10">
@@ -545,11 +545,11 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9939</v>
+        <v>0.9407</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9749 – 1.0129</t>
+          <t>0.7752 – 1.1369</t>
         </is>
       </c>
       <c r="D11">
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.9939</v>
+        <v>0.9408</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9753 – 1.0124</t>
+          <t>0.7788 – 1.1315</t>
         </is>
       </c>
       <c r="D12">
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.9919</v>
+        <v>0.922</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.9741 – 1.0095</t>
+          <t>0.7694 – 1.0995</t>
         </is>
       </c>
       <c r="D13">
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.9966</v>
+        <v>0.9661</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.9816 – 1.0114</t>
+          <t>0.8306 – 1.1205</t>
         </is>
       </c>
       <c r="D14">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.9991</v>
+        <v>0.9908</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.9827 – 1.0156</t>
+          <t>0.8394 – 1.1679</t>
         </is>
       </c>
       <c r="D15">
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.0044</v>
+        <v>1.0445</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.9892 – 1.0197</t>
+          <t>0.8973 – 1.2157</t>
         </is>
       </c>
       <c r="D16">
@@ -653,11 +653,11 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.0072</v>
+        <v>1.074</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.9921 – 1.0225</t>
+          <t>0.9241 – 1.2486</t>
         </is>
       </c>
       <c r="D17">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.998</v>
+        <v>0.9806</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.9826 – 1.0135</t>
+          <t>0.8392 – 1.1436</t>
         </is>
       </c>
       <c r="D18">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.9989</v>
+        <v>0.9889</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.9844 – 1.0133</t>
+          <t>0.8549 – 1.1415</t>
         </is>
       </c>
       <c r="D19">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.9971</v>
+        <v>0.971</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9829 – 1.0112</t>
+          <t>0.8416 – 1.1174</t>
         </is>
       </c>
       <c r="D20">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.9937</v>
+        <v>0.9389</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.9802 – 1.0071</t>
+          <t>0.8188 – 1.0737</t>
         </is>
       </c>
       <c r="D21">
@@ -743,11 +743,11 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.9957</v>
+        <v>0.9577</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.9732 – 1.0184</t>
+          <t>0.7621 – 1.1995</t>
         </is>
       </c>
       <c r="D22">
@@ -761,11 +761,11 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.9956</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.9746 – 1.0168</t>
+          <t>0.7731 – 1.1811</t>
         </is>
       </c>
       <c r="D23">
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.9965000000000001</v>
+        <v>0.9654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.9771 – 1.0159</t>
+          <t>0.793 – 1.1705</t>
         </is>
       </c>
       <c r="D24">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.9939</v>
+        <v>0.9406</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9752 – 1.0125</t>
+          <t>0.7781 – 1.1328</t>
         </is>
       </c>
       <c r="D25">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.9981</v>
+        <v>0.9813</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.9827 – 1.0135</t>
+          <t>0.8402 – 1.1439</t>
         </is>
       </c>
       <c r="D26">
@@ -833,11 +833,11 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.9985000000000001</v>
+        <v>0.9852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.9841 – 1.0129</t>
+          <t>0.852 – 1.1368</t>
         </is>
       </c>
       <c r="D27">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.9971</v>
+        <v>0.9712</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.983 – 1.0111</t>
+          <t>0.8423 – 1.1171</t>
         </is>
       </c>
       <c r="D28">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.9936</v>
+        <v>0.9377</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.9801 – 1.007</t>
+          <t>0.8178 – 1.0722</t>
         </is>
       </c>
       <c r="D29">
